--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_19_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_19_Trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5381A9-ADE3-4DD1-9D2F-E553B447F8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36FAEA7-1B16-472E-8A6E-7ECAF5043C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,61 +55,91 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT ADANIENT 28 Aug 2025 2350 CE</t>
-  </si>
-  <si>
-    <t>19-08-2025</t>
-  </si>
-  <si>
-    <t>OPT HINDUNILVR 28 Aug 2025 2600 CE</t>
-  </si>
-  <si>
-    <t>20-08-2025</t>
-  </si>
-  <si>
-    <t>OPT PGEL 28 Aug 2025 560 CE</t>
-  </si>
-  <si>
-    <t>OPT KAYNES 28 Aug 2025 6200 PE</t>
-  </si>
-  <si>
-    <t>OPT KEI 28 Aug 2025 4000 CE</t>
-  </si>
-  <si>
-    <t>OPT TCS 28 Aug 2025 3100 CE</t>
-  </si>
-  <si>
-    <t>21-08-2025</t>
-  </si>
-  <si>
-    <t>OPT MANKIND 28 Aug 2025 2500 CE</t>
-  </si>
-  <si>
-    <t>OPT TATAELXSI 28 Aug 2025 5700 PE</t>
-  </si>
-  <si>
-    <t>OPT ALKEM 28 Aug 2025 5400 CE</t>
-  </si>
-  <si>
-    <t>OPT HAL 28 Aug 2025 4500 CE</t>
-  </si>
-  <si>
-    <t>OPT TATAELXSI 28 Aug 2025 5600 CE</t>
-  </si>
-  <si>
-    <t>22-08-2025</t>
-  </si>
-  <si>
-    <t>OPT LAURUSLABS 28 Aug 2025 890 PE</t>
-  </si>
-  <si>
-    <t>OPT TIINDIA 28 Aug 2025 3200 CE</t>
-  </si>
-  <si>
-    <t>OPT LAURUSLABS 28 Aug 2025 890 CE</t>
-  </si>
-  <si>
-    <t>OPT INDHOTEL 28 Aug 2025 800 PE</t>
+    <t>OPT MAZDOCK 30 Sep 2025 3000 CE</t>
+  </si>
+  <si>
+    <t>22-09-2025</t>
+  </si>
+  <si>
+    <t>OPT PNB 30 Sep 2025 114 CE</t>
+  </si>
+  <si>
+    <t>OPT HUDCO 30 Sep 2025 230 CE</t>
+  </si>
+  <si>
+    <t>OPT ADANIGREEN 30 Sep 2025 1060 CE</t>
+  </si>
+  <si>
+    <t>OPT SBIN 30 Sep 2025 860 CE</t>
+  </si>
+  <si>
+    <t>OPT DMART 30 Sep 2025 4600 PE</t>
+  </si>
+  <si>
+    <t>23-09-2025</t>
+  </si>
+  <si>
+    <t>OPT ASHOKLEY 30 Sep 2025 140 CE</t>
+  </si>
+  <si>
+    <t>OPT ADANIENT 30 Sep 2025 2600 CE</t>
+  </si>
+  <si>
+    <t>OPT AXISBANK 30 Sep 2025 1150 CE</t>
+  </si>
+  <si>
+    <t>OPT MOTHERSON 30 Sep 2025 110 CE</t>
+  </si>
+  <si>
+    <t>OPT POLYCAB 30 Sep 2025 7600 CE</t>
+  </si>
+  <si>
+    <t>OPT ADANIGREEN 30 Sep 2025 1160 CE</t>
+  </si>
+  <si>
+    <t>OPT EICHERMOT 30 Sep 2025 7000 CE</t>
+  </si>
+  <si>
+    <t>24-09-2025</t>
+  </si>
+  <si>
+    <t>OPT COFORGE 30 Sep 2025 1660 PE</t>
+  </si>
+  <si>
+    <t>OPT OIL 30 Sep 2025 420 CE</t>
+  </si>
+  <si>
+    <t>25-09-2025</t>
+  </si>
+  <si>
+    <t>OPT JSWSTEEL 30 Sep 2025 1150 CE</t>
+  </si>
+  <si>
+    <t>OPT POLYCAB 30 Sep 2025 7500 PE</t>
+  </si>
+  <si>
+    <t>OPT ONGC 30 Sep 2025 240 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 30 Sep 2025 25000 PE</t>
+  </si>
+  <si>
+    <t>OPT TATAMOTORS 30 Sep 2025 660 PE</t>
+  </si>
+  <si>
+    <t>OPT INOXWIND 30 Sep 2025 145 CE</t>
+  </si>
+  <si>
+    <t>OPT ZYDUSLIFE 28 Oct 2025 1000 PE</t>
+  </si>
+  <si>
+    <t>26-09-2025</t>
+  </si>
+  <si>
+    <t>OPT JSWSTEEL 28 Oct 2025 1150 PE</t>
+  </si>
+  <si>
+    <t>OPT ALKEM 28 Oct 2025 5000 PE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -462,10 +492,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -481,10 +511,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -493,10 +523,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -519,707 +549,1130 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>3</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45888</v>
+        <v>45922</v>
       </c>
       <c r="D2">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="E2">
-        <v>54</v>
+        <v>83.45</v>
       </c>
       <c r="F2">
-        <v>16200</v>
+        <v>14603.75</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="I2">
-        <v>58</v>
+        <v>92.65</v>
       </c>
       <c r="J2">
-        <v>17400</v>
+        <v>16213.75</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1200</v>
+        <v>1610</v>
       </c>
       <c r="M2">
-        <v>78.319999999999993</v>
+        <v>76.81</v>
       </c>
       <c r="N2">
-        <v>1121.68</v>
+        <v>1533.19</v>
       </c>
       <c r="O2">
-        <v>1200</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>121</v>
+        <v>234</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45889</v>
+        <v>45922</v>
       </c>
       <c r="D3">
-        <v>300</v>
+        <v>8000</v>
       </c>
       <c r="E3">
-        <v>51.5</v>
+        <v>2.25</v>
       </c>
       <c r="F3">
-        <v>15450</v>
+        <v>18000</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>300</v>
+        <v>8000</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>2550</v>
+        <v>-2000</v>
       </c>
       <c r="M3">
-        <v>79.72</v>
+        <v>78.03</v>
       </c>
       <c r="N3">
-        <v>2470.2800000000002</v>
+        <v>-2078.0300000000002</v>
       </c>
       <c r="O3">
-        <v>2550</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>231</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>45889</v>
+        <v>45922</v>
       </c>
       <c r="D4">
-        <v>700</v>
+        <v>2775</v>
       </c>
       <c r="E4">
-        <v>24.3</v>
+        <v>6.65</v>
       </c>
       <c r="F4">
-        <v>17010</v>
+        <v>18453.75</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>700</v>
+        <v>2775</v>
       </c>
       <c r="I4">
-        <v>22.45</v>
+        <v>6.85</v>
       </c>
       <c r="J4">
-        <v>15715</v>
+        <v>19008.75</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>-1295</v>
+        <v>555</v>
       </c>
       <c r="M4">
-        <v>77.19</v>
+        <v>82.51</v>
       </c>
       <c r="N4">
-        <v>-1372.19</v>
+        <v>472.49</v>
       </c>
       <c r="O4">
-        <v>1295</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>45889</v>
+        <v>45922</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E5">
-        <v>113</v>
+        <v>41.4</v>
       </c>
       <c r="F5">
-        <v>11300</v>
+        <v>24840</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="J5">
-        <v>10000</v>
+        <v>28800</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-1300</v>
+        <v>3960</v>
       </c>
       <c r="M5">
-        <v>66.5</v>
+        <v>100.07</v>
       </c>
       <c r="N5">
-        <v>-1366.5</v>
+        <v>3859.93</v>
       </c>
       <c r="O5">
-        <v>1300</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>158</v>
+        <v>251</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1">
-        <v>45889</v>
+        <v>45922</v>
       </c>
       <c r="D6">
-        <v>175</v>
+        <v>750</v>
       </c>
       <c r="E6">
-        <v>111</v>
+        <v>12.4</v>
       </c>
       <c r="F6">
-        <v>19425</v>
+        <v>9300</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>175</v>
+        <v>750</v>
       </c>
       <c r="I6">
-        <v>105</v>
+        <v>12.85</v>
       </c>
       <c r="J6">
-        <v>18375</v>
+        <v>9637.5</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>-1050</v>
+        <v>337.5</v>
       </c>
       <c r="M6">
-        <v>82.07</v>
+        <v>65.08</v>
       </c>
       <c r="N6">
-        <v>-1132.07</v>
+        <v>272.42</v>
       </c>
       <c r="O6">
-        <v>1050</v>
+        <v>337.5</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>275</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45923</v>
+      </c>
+      <c r="D7">
+        <v>150</v>
+      </c>
+      <c r="E7">
+        <v>86</v>
+      </c>
+      <c r="F7">
+        <v>12900</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1">
-        <v>45890</v>
-      </c>
-      <c r="D7">
-        <v>175</v>
-      </c>
-      <c r="E7">
-        <v>32.4</v>
-      </c>
-      <c r="F7">
-        <v>5670</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="H7">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I7">
-        <v>36.4</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="J7">
-        <v>6370</v>
+        <v>10027.5</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>700</v>
+        <v>-2872.5</v>
       </c>
       <c r="M7">
-        <v>58.8</v>
+        <v>67.260000000000005</v>
       </c>
       <c r="N7">
-        <v>641.20000000000005</v>
+        <v>-2939.76</v>
       </c>
       <c r="O7">
-        <v>700</v>
+        <v>2872.5</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>45890</v>
+        <v>45923</v>
       </c>
       <c r="D8">
-        <v>225</v>
+        <v>5000</v>
       </c>
       <c r="E8">
-        <v>97.5</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>21937.5</v>
+        <v>20000</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8">
-        <v>225</v>
+        <v>5000</v>
       </c>
       <c r="I8">
-        <v>104.15</v>
+        <v>3.65</v>
       </c>
       <c r="J8">
-        <v>23433.75</v>
+        <v>18250</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1496.25</v>
+        <v>-1750</v>
       </c>
       <c r="M8">
-        <v>90.09</v>
+        <v>82.13</v>
       </c>
       <c r="N8">
-        <v>1406.16</v>
+        <v>-1832.13</v>
       </c>
       <c r="O8">
-        <v>1496.25</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>263</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1">
-        <v>45890</v>
+        <v>45923</v>
       </c>
       <c r="D9">
+        <v>300</v>
+      </c>
+      <c r="E9">
         <v>100</v>
       </c>
-      <c r="E9">
-        <v>85</v>
-      </c>
       <c r="F9">
-        <v>8500</v>
+        <v>30000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I9">
-        <v>87</v>
+        <v>105.6</v>
       </c>
       <c r="J9">
-        <v>8700</v>
+        <v>31680</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>200</v>
+        <v>1680</v>
       </c>
       <c r="M9">
-        <v>63.39</v>
+        <v>105.79</v>
       </c>
       <c r="N9">
-        <v>136.61000000000001</v>
+        <v>1574.21</v>
       </c>
       <c r="O9">
-        <v>200</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1">
-        <v>45890</v>
+        <v>45923</v>
       </c>
       <c r="D10">
-        <v>125</v>
+        <v>625</v>
       </c>
       <c r="E10">
-        <v>96.7</v>
+        <v>13.5</v>
       </c>
       <c r="F10">
-        <v>12087.5</v>
+        <v>8437.5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10">
-        <v>125</v>
+        <v>625</v>
       </c>
       <c r="I10">
-        <v>99.45</v>
+        <v>14.55</v>
       </c>
       <c r="J10">
-        <v>12431.25</v>
+        <v>9093.75</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>343.75</v>
+        <v>656.25</v>
       </c>
       <c r="M10">
-        <v>70.3</v>
+        <v>63.91</v>
       </c>
       <c r="N10">
-        <v>273.45</v>
+        <v>592.34</v>
       </c>
       <c r="O10">
-        <v>343.75</v>
+        <v>656.25</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
-        <v>45890</v>
+        <v>45923</v>
       </c>
       <c r="D11">
-        <v>150</v>
+        <v>6150</v>
       </c>
       <c r="E11">
-        <v>86.75</v>
+        <v>3.05</v>
       </c>
       <c r="F11">
-        <v>13012.5</v>
+        <v>18757.5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11">
-        <v>150</v>
+        <v>6150</v>
       </c>
       <c r="I11">
-        <v>76.650000000000006</v>
+        <v>2.65</v>
       </c>
       <c r="J11">
-        <v>11497.5</v>
+        <v>16297.5</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>-1515</v>
+        <v>-2460</v>
       </c>
       <c r="M11">
-        <v>69.400000000000006</v>
+        <v>78.8</v>
       </c>
       <c r="N11">
-        <v>-1584.4</v>
+        <v>-2538.8000000000002</v>
       </c>
       <c r="O11">
-        <v>1515</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1">
-        <v>45891</v>
+        <v>45923</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E12">
-        <v>68</v>
+        <v>136.85</v>
       </c>
       <c r="F12">
-        <v>6800</v>
+        <v>17106.25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I12">
-        <v>61.9</v>
+        <v>125</v>
       </c>
       <c r="J12">
-        <v>6190</v>
+        <v>15625</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>-610</v>
+        <v>-1481.25</v>
       </c>
       <c r="M12">
-        <v>59.05</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="N12">
-        <v>-669.05</v>
+        <v>-1558.35</v>
       </c>
       <c r="O12">
-        <v>610</v>
+        <v>1481.25</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1">
-        <v>45891</v>
+        <v>45923</v>
       </c>
       <c r="D13">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="E13">
-        <v>14.8</v>
+        <v>42.48</v>
       </c>
       <c r="F13">
-        <v>25160</v>
+        <v>50970</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H13">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="I13">
-        <v>13.1</v>
+        <v>25.18</v>
       </c>
       <c r="J13">
-        <v>22270</v>
+        <v>30210</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>-2890</v>
+        <v>-20760</v>
       </c>
       <c r="M13">
-        <v>89.45</v>
+        <v>136.66999999999999</v>
       </c>
       <c r="N13">
-        <v>-2979.45</v>
+        <v>-20896.669999999998</v>
       </c>
       <c r="O13">
-        <v>2890</v>
+        <v>20760</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1">
-        <v>45891</v>
+        <v>45924</v>
       </c>
       <c r="D14">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E14">
-        <v>48</v>
+        <v>120.9</v>
       </c>
       <c r="F14">
-        <v>9600</v>
+        <v>21157.5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="I14">
-        <v>36.5</v>
+        <v>95.45</v>
       </c>
       <c r="J14">
-        <v>7300</v>
+        <v>16703.75</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>-2300</v>
+        <v>-4453.75</v>
       </c>
       <c r="M14">
-        <v>61.9</v>
+        <v>80.87</v>
       </c>
       <c r="N14">
-        <v>-2361.9</v>
+        <v>-4534.62</v>
       </c>
       <c r="O14">
-        <v>2300</v>
+        <v>4453.75</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1">
-        <v>45891</v>
+        <v>45924</v>
       </c>
       <c r="D15">
-        <v>1700</v>
+        <v>375</v>
       </c>
       <c r="E15">
-        <v>11.4</v>
+        <v>40.1</v>
       </c>
       <c r="F15">
-        <v>19380</v>
+        <v>15037.5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15">
-        <v>1700</v>
+        <v>375</v>
       </c>
       <c r="I15">
-        <v>11.6</v>
+        <v>34.15</v>
       </c>
       <c r="J15">
-        <v>19720</v>
+        <v>12806.25</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>340</v>
+        <v>-2231.25</v>
       </c>
       <c r="M15">
-        <v>83.94</v>
+        <v>72.17</v>
       </c>
       <c r="N15">
-        <v>256.06</v>
+        <v>-2303.42</v>
       </c>
       <c r="O15">
-        <v>340</v>
+        <v>2231.25</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D16">
+        <v>1400</v>
+      </c>
+      <c r="E16">
+        <v>7.65</v>
+      </c>
+      <c r="F16">
+        <v>10710</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="1">
-        <v>45891</v>
-      </c>
-      <c r="D16">
-        <v>1000</v>
-      </c>
-      <c r="E16">
-        <v>13.65</v>
-      </c>
-      <c r="F16">
-        <v>13650</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="H16">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="I16">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="J16">
-        <v>14000</v>
+        <v>9100</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>350</v>
+        <v>-1610</v>
       </c>
       <c r="M16">
-        <v>73.239999999999995</v>
+        <v>64.95</v>
       </c>
       <c r="N16">
-        <v>276.76</v>
+        <v>-1674.95</v>
       </c>
       <c r="O16">
-        <v>350</v>
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>149</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D17">
+        <v>675</v>
+      </c>
+      <c r="E17">
+        <v>15.4</v>
+      </c>
+      <c r="F17">
+        <v>10395</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17">
+        <v>675</v>
+      </c>
+      <c r="I17">
+        <v>12.45</v>
+      </c>
+      <c r="J17">
+        <v>8403.75</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>-1991.25</v>
+      </c>
+      <c r="M17">
+        <v>63.81</v>
+      </c>
+      <c r="N17">
+        <v>-2055.06</v>
+      </c>
+      <c r="O17">
+        <v>1991.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>239</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D18">
+        <v>250</v>
+      </c>
+      <c r="E18">
+        <v>101.8</v>
+      </c>
+      <c r="F18">
+        <v>25450</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18">
+        <v>250</v>
+      </c>
+      <c r="I18">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="J18">
+        <v>20225</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>-5225</v>
+      </c>
+      <c r="M18">
+        <v>134.43</v>
+      </c>
+      <c r="N18">
+        <v>-5359.43</v>
+      </c>
+      <c r="O18">
+        <v>5225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>223</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D19">
+        <v>2250</v>
+      </c>
+      <c r="E19">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F19">
+        <v>5512.5</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19">
+        <v>2250</v>
+      </c>
+      <c r="I19">
+        <v>1.9</v>
+      </c>
+      <c r="J19">
+        <v>4275</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>-1237.5</v>
+      </c>
+      <c r="M19">
+        <v>55.77</v>
+      </c>
+      <c r="N19">
+        <v>-1293.27</v>
+      </c>
+      <c r="O19">
+        <v>1237.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D20">
+        <v>150</v>
+      </c>
+      <c r="E20">
+        <v>77.95</v>
+      </c>
+      <c r="F20">
+        <v>11692.5</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20">
+        <v>150</v>
+      </c>
+      <c r="I20">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="J20">
+        <v>10140</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>-1552.5</v>
+      </c>
+      <c r="M20">
+        <v>90.47</v>
+      </c>
+      <c r="N20">
+        <v>-1642.97</v>
+      </c>
+      <c r="O20">
+        <v>1552.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>268</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D21">
+        <v>800</v>
+      </c>
+      <c r="E21">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>6400</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21">
+        <v>800</v>
+      </c>
+      <c r="I21">
+        <v>7.4</v>
+      </c>
+      <c r="J21">
+        <v>5920</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>-480</v>
+      </c>
+      <c r="M21">
+        <v>58.49</v>
+      </c>
+      <c r="N21">
+        <v>-538.49</v>
+      </c>
+      <c r="O21">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D22">
+        <v>3272</v>
+      </c>
+      <c r="E22">
+        <v>3.15</v>
+      </c>
+      <c r="F22">
+        <v>10306.799999999999</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22">
+        <v>3272</v>
+      </c>
+      <c r="I22">
+        <v>2.35</v>
+      </c>
+      <c r="J22">
+        <v>7689.2</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>-2617.6</v>
+      </c>
+      <c r="M22">
+        <v>62.77</v>
+      </c>
+      <c r="N22">
+        <v>-2680.37</v>
+      </c>
+      <c r="O22">
+        <v>2617.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>292</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D23">
+        <v>900</v>
+      </c>
+      <c r="E23">
+        <v>32.35</v>
+      </c>
+      <c r="F23">
+        <v>29115</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23">
+        <v>900</v>
+      </c>
+      <c r="I23">
+        <v>27.8</v>
+      </c>
+      <c r="J23">
+        <v>25020</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>-4095</v>
+      </c>
+      <c r="M23">
+        <v>96.46</v>
+      </c>
+      <c r="N23">
+        <v>-4191.46</v>
+      </c>
+      <c r="O23">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>150</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D24">
+        <v>675</v>
+      </c>
+      <c r="E24">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="F24">
+        <v>25683.75</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24">
+        <v>675</v>
+      </c>
+      <c r="I24">
+        <v>37</v>
+      </c>
+      <c r="J24">
+        <v>24975</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>-708.75</v>
+      </c>
+      <c r="M24">
+        <v>94.25</v>
+      </c>
+      <c r="N24">
+        <v>-803</v>
+      </c>
+      <c r="O24">
+        <v>708.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D25">
+        <v>125</v>
+      </c>
+      <c r="E25">
+        <v>26.25</v>
+      </c>
+      <c r="F25">
+        <v>3281.25</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25">
+        <v>125</v>
+      </c>
+      <c r="I25">
+        <v>21.15</v>
+      </c>
+      <c r="J25">
+        <v>2643.75</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>-637.5</v>
+      </c>
+      <c r="M25">
+        <v>52.43</v>
+      </c>
+      <c r="N25">
+        <v>-689.93</v>
+      </c>
+      <c r="O25">
+        <v>637.5</v>
       </c>
     </row>
   </sheetData>
